--- a/artfynd/A 61503-2022 artfynd.xlsx
+++ b/artfynd/A 61503-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61503-2022 artfynd.xlsx
+++ b/artfynd/A 61503-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>168766</v>
+        <v>104441</v>
       </c>
       <c r="B2" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,12 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>68</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -725,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sågtorp, O om, Srm</t>
+          <t>Näshulta sn, Nytorp, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575958.188822814</v>
+        <v>575988</v>
       </c>
       <c r="R2" t="n">
-        <v>6561135.05914464</v>
+        <v>6561116</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,22 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-07-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-20</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sluttning mot söder, norr om väg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,7 +773,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Skogsbryn mot väg</t>
+          <t>Skogssluttning mot väg</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -799,22 +784,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Gustafson, Bo Karlsson</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>168768</v>
+        <v>104442</v>
       </c>
       <c r="B3" t="n">
-        <v>104643</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,12 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -856,14 +831,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sågtorp, O om, Srm</t>
+          <t>Näshulta sn, Nytorp, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575997.9174681213</v>
+        <v>575998</v>
       </c>
       <c r="R3" t="n">
-        <v>6561125.599005444</v>
+        <v>6561111</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -890,22 +865,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-07-04</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-07-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2004-07-20</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Söder om väg</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +889,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Dike mellan väg och åker</t>
+          <t>Vägkant mot vall</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -930,22 +900,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Gustafson, Bo Karlsson</t>
+          <t>Håkan Gustafson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>60493331</v>
+        <v>168765</v>
       </c>
       <c r="B4" t="n">
-        <v>106964</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,16 +918,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220299</v>
+        <v>245</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -970,17 +935,31 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Svalboviken, Sågtorp, Srm</t>
+          <t>Sågtorp, O om, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575959.7454739227</v>
+        <v>575948</v>
       </c>
       <c r="R4" t="n">
-        <v>6561005.400135099</v>
+        <v>6561115</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,22 +986,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2016-07-03</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2016-07-03</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-07-04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,7 +1005,7 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>Skogsbryn mot väg</t>
+          <t>Dike mellan väg och åker</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1047,22 +1016,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Gustafson</t>
+          <t>Håkan Gustafson, Bo Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87015259</v>
+        <v>168766</v>
       </c>
       <c r="B5" t="n">
-        <v>44335</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1070,57 +1034,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102021</v>
+        <v>245</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Skogsklocka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Campanula cervicaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>ex.</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Nytorp 2, Eskilstuna, Srm</t>
+          <t>Sågtorp, O om, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575983.1057489648</v>
+        <v>575958</v>
       </c>
       <c r="R5" t="n">
-        <v>6561147.345532569</v>
+        <v>6561135</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1144,22 +1102,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2011-07-04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-07-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:00</t>
+          <t>2011-07-04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1170,19 +1118,1040 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Skogsbryn mot väg</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>168767</v>
+      </c>
+      <c r="B6" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>245</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sågtorp, O om, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>575978</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6561126</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2011-07-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2011-07-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Dike mellan väg och åker</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>168768</v>
+      </c>
+      <c r="B7" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>245</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sågtorp, O om, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>575998</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6561126</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2011-07-04</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2011-07-04</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Dike mellan väg och åker</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson, Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>60493323</v>
+      </c>
+      <c r="B8" t="n">
+        <v>107708</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>245</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Skogsklocka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Campanula cervicaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Svalboviken, Nyberga, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>575802</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6560834</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2016-07-03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2016-07-03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Vägkant mot åker</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110593451</v>
+      </c>
+      <c r="B9" t="n">
+        <v>43212</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>101070</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Silversmygare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hesperia comma</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kråksten, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>575960</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6561127</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-07-04</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:47</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Johan Mellquist</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Johan Mellquist, Joachim Strengbom</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>87015259</v>
+      </c>
+      <c r="B10" t="n">
+        <v>45049</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102021</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Zygaena viciae</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Nytorp 2, Eskilstuna, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>575983</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6561147</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-07-21</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-07-21</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Thomas Holmgren</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Thomas Holmgren</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>86361257</v>
+      </c>
+      <c r="B11" t="n">
+        <v>108194</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220103</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Klasefibbla</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Crepis praemorsa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Walther</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Nyberga, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>575841</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6560884</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-06-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-06-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Vägkant mot åkermark</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>60493331</v>
+      </c>
+      <c r="B12" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Svalboviken, Sågtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>575960</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6561005</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2016-07-03</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2016-07-03</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Skogsbryn mot väg</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>86361258</v>
+      </c>
+      <c r="B13" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Nyberga, NO om, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>575841</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6560884</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2020-06-07</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2020-06-07</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Vägkant mot åkermark</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>60493342</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Svalboviken, Sågtorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>575960</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6561005</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Eskilstuna</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Näshulta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2016-07-03</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2016-07-03</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Vägkant</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Håkan Gustafson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61503-2022 artfynd.xlsx
+++ b/artfynd/A 61503-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104441</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -904,6 +914,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104442</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/168765</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/168766</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1277,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/168767</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1368,6 +1398,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/168768</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1487,6 +1522,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60493323</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1598,6 +1638,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110593451</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1725,6 +1770,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87015259</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1841,6 +1891,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86361257</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1943,6 +1998,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60493331</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2050,6 +2110,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86361258</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2152,8 +2217,28 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60493342</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>